--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -422,17 +422,17 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 9 3층 비플로우</t>
+          <t>��원 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -726,10 +726,10 @@
         <v>374</v>
       </c>
       <c r="Q3" t="n">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="R3" t="n">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>노익스짐 PT</t>
+          <t>핏앤피트니스 PT &amp; 그룹피티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>no_x_gym@naver.com</t>
+          <t>ssz1549@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1486-6692</t>
+          <t>0507-1445-0383</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/no_x_gym</t>
+          <t>https://www.youtube.com/@hipupschool</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4047s</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="Q4" t="n">
-        <v>858</v>
+        <v>776</v>
       </c>
       <c r="R4" t="n">
-        <v>1135</v>
+        <v>1015</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1213015794</t>
+          <t>1793276177</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213015794</t>
+          <t>https://m.place.naver.com/place/1793276177</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>핏앤피트니스 PT &amp; 그룹피티</t>
+          <t>노익스짐 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ssz1549@naver.com</t>
+          <t>no_x_gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1445-0383</t>
+          <t>0507-1486-6692</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@hipupschool</t>
+          <t>https://blog.naver.com/no_x_gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,19 +895,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4047s</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="Q5" t="n">
-        <v>776</v>
+        <v>859</v>
       </c>
       <c r="R5" t="n">
-        <v>1015</v>
+        <v>1138</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1793276177</t>
+          <t>1213015794</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793276177</t>
+          <t>https://m.place.naver.com/place/1213015794</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>필라테슈</t>
+          <t>바른체형코칭센터 무실점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>qnfnalsl@naver.com</t>
+          <t>youha3888@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1317-3140</t>
+          <t>0507-1335-3473</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 웅비3길 7 1층</t>
+          <t>강원 원주시 능라동길 72 4층 402호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pilatesue_private1</t>
+          <t>https://blog.naver.com/youha3888/223757800783</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49uvt</t>
+          <t>https://talk.naver.com/ct/wq3h9yk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="R7" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1389480176</t>
+          <t>2058717725</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389480176</t>
+          <t>https://m.place.naver.com/place/2058717725</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>혁신런앤핏</t>
+          <t>필라테슈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hghghghg00@naver.com</t>
+          <t>qnfnalsl@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1346-7262</t>
+          <t>0507-1317-3140</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 혁신로 19 지하층 101호</t>
+          <t>강원 원주시 웅비3길 7 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hs_run_fit</t>
+          <t>https://www.instagram.com/pilatesue_private1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1186,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49uvt</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="R8" t="n">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1223719800</t>
+          <t>1389480176</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223719800</t>
+          <t>https://m.place.naver.com/place/1389480176</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1233,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>클래식짐 PT 혁신점</t>
+          <t>팀키스짐 &amp; PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>classicgym2749@naver.com</t>
+          <t>teamkis_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1313-2749</t>
+          <t>0507-1399-2305</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 황금로 20 5층 502호</t>
+          <t>강원 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/classicgym2749</t>
+          <t>https://blog.naver.com/teamkis_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ae4e</t>
+          <t>https://talk.naver.com/ct/w4olwd</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>76</v>
+        <v>2310</v>
       </c>
       <c r="Q9" t="n">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="R9" t="n">
-        <v>160</v>
+        <v>2806</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1324878145</t>
+          <t>1433616376</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324878145</t>
+          <t>https://m.place.naver.com/place/1433616376</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>��원 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q2" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="R2" t="n">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>노익스짐 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>no_x_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1354-8955</t>
+          <t>0507-1486-6692</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://blog.naver.com/no_x_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +699,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>374</v>
+        <v>283</v>
       </c>
       <c r="Q3" t="n">
-        <v>2136</v>
+        <v>863</v>
       </c>
       <c r="R3" t="n">
-        <v>2510</v>
+        <v>1146</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>1213015794</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/1213015794</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>핏앤피트니스 PT &amp; 그룹피티</t>
+          <t>비브레 PT\u002F헬스 혁신점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ssz1549@naver.com</t>
+          <t>wonju_ht@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1445-0383</t>
+          <t>0507-1354-8955</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@hipupschool</t>
+          <t>http://vivre-training.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4047s</t>
+          <t>https://talk.naver.com/ct/w46eja</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>239</v>
+        <v>378</v>
       </c>
       <c r="Q4" t="n">
-        <v>776</v>
+        <v>2174</v>
       </c>
       <c r="R4" t="n">
-        <v>1015</v>
+        <v>2552</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1793276177</t>
+          <t>1193233179</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793276177</t>
+          <t>https://m.place.naver.com/place/1193233179</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>노익스짐 PT</t>
+          <t>핏앤피트니스 PT &amp; 그룹피티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>no_x_gym@naver.com</t>
+          <t>ssz1549@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1486-6692</t>
+          <t>0507-1445-0383</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/no_x_gym</t>
+          <t>https://www.youtube.com/@hipupschool</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,15 +891,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4047s</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="Q5" t="n">
-        <v>859</v>
+        <v>778</v>
       </c>
       <c r="R5" t="n">
-        <v>1138</v>
+        <v>1016</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1213015794</t>
+          <t>1793276177</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213015794</t>
+          <t>https://m.place.naver.com/place/1793276177</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -952,44 +952,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>핏앤피트니스 혁신점</t>
+          <t>혁신런앤핏</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ssb154911@naver.com</t>
+          <t>hghghghg00@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>033-735-0302</t>
+          <t>0507-1346-7262</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 미래로 1 강림빌딩 3층 302호</t>
+          <t>강원 원주시 혁신로 19 지하층 101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://fitandfitness.imweb.me</t>
+          <t>https://www.instagram.com/hs_run_fit</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>284</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
-        <v>406</v>
+        <v>23</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1042681042</t>
+          <t>1223719800</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1042681042</t>
+          <t>https://m.place.naver.com/place/1223719800</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q7" t="n">
         <v>52</v>
       </c>
       <c r="R7" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2310</v>
+        <v>2319</v>
       </c>
       <c r="Q9" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="R9" t="n">
-        <v>2806</v>
+        <v>2819</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1328,7 +1328,105 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>바디라인휘트니스 원주무실점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bodyline2@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1428-3415</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>강원 원주시 능라동길 48-1 5층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyline2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4loqz</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>714</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>724</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1438</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1140023595</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140023595</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bflowpt@naver.com</t>
+          <t>b-flowgym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bflowpt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>노익스짐 PT</t>
+          <t>비브레 PT/헬스 혁신점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>no_x_gym@naver.com</t>
+          <t>gjwodbs7@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1486-6692</t>
+          <t>0507-1354-8955</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/no_x_gym</t>
+          <t>http://vivre-training.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eja</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>283</v>
+        <v>378</v>
       </c>
       <c r="Q3" t="n">
-        <v>863</v>
+        <v>2178</v>
       </c>
       <c r="R3" t="n">
-        <v>1146</v>
+        <v>2556</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1213015794</t>
+          <t>1193233179</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213015794</t>
+          <t>https://m.place.naver.com/place/1193233179</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>노익스짐 PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>no_x_gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1354-8955</t>
+          <t>0507-1486-6692</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://blog.naver.com/no_x_gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,19 +797,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>378</v>
+        <v>287</v>
       </c>
       <c r="Q4" t="n">
-        <v>2174</v>
+        <v>864</v>
       </c>
       <c r="R4" t="n">
-        <v>2552</v>
+        <v>1151</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>1213015794</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/1213015794</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +896,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4047s</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -969,7 +965,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 혁신로 19 지하층 101호</t>
+          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1034,7 +1030,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1046,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바른체형코칭센터 무실점</t>
+          <t>필라테슈</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>youha3888@naver.com</t>
+          <t>qnfnalsl@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1335-3473</t>
+          <t>0507-1317-3140</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 72 4층 402호</t>
+          <t>강원 원주시 웅비3길 7 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youha3888/223757800783</t>
+          <t>https://www.instagram.com/pilatesue_private1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wq3h9yk</t>
+          <t>https://talk.naver.com/ct/w49uvt</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="Q7" t="n">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,51 +1118,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2058717725</t>
+          <t>1389480176</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058717725</t>
+          <t>https://m.place.naver.com/place/1389480176</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>필라테슈</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>qnfnalsl@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1317-3140</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 웅비3길 7 1층</t>
+          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pilatesue_private1</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,19 +1177,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49uvt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>717</v>
       </c>
       <c r="Q8" t="n">
-        <v>121</v>
+        <v>727</v>
       </c>
       <c r="R8" t="n">
-        <v>184</v>
+        <v>1444</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,213 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1389480176</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389480176</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>팀키스짐 &amp; PT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>teamkis_@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1399-2305</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>강원 원주시 능라동길 26 4층</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/teamkis_</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4olwd</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>2319</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>500</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2819</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1433616376</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1433616376</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>바디라인휘트니스 원주무실점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bodyline2@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1428-3415</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bodyline2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>714</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>724</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1438</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1140023595</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>b-flowgym@naver.com</t>
+          <t>bflowpt@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bflowpt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h9q7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -667,7 +663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gjwodbs7@naver.com</t>
+          <t>wonju_ht@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -1140,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>팀키스짐 &amp; PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>teamkis_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1399-2305</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
+          <t>강원특별자치도 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://blog.naver.com/teamkis_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1197,30 +1189,124 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>2327</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>500</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2827</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1433616376</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1433616376</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>바디라인휘트니스 원주무실점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bodyline2@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1428-3415</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyline2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>717</v>
       </c>
-      <c r="Q8" t="n">
-        <v>727</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1444</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>729</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1446</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>1140023595</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h9q7</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비브레 PT/헬스 혁신점</t>
+          <t>노익스짐 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>no_x_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1354-8955</t>
+          <t>0507-1486-6692</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://blog.naver.com/no_x_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>378</v>
+        <v>287</v>
       </c>
       <c r="Q3" t="n">
-        <v>2178</v>
+        <v>864</v>
       </c>
       <c r="R3" t="n">
-        <v>2556</v>
+        <v>1151</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>1213015794</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/1213015794</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>노익스짐 PT</t>
+          <t>비브레 PT\u002F헬스 혁신점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>no_x_gym@naver.com</t>
+          <t>wonju_ht@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1486-6692</t>
+          <t>0507-1354-8955</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/no_x_gym</t>
+          <t>http://vivre-training.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,15 +793,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eja</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>287</v>
+        <v>378</v>
       </c>
       <c r="Q4" t="n">
-        <v>864</v>
+        <v>2178</v>
       </c>
       <c r="R4" t="n">
-        <v>1151</v>
+        <v>2556</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1213015794</t>
+          <t>1193233179</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213015794</t>
+          <t>https://m.place.naver.com/place/1193233179</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4047s</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
+          <t>강원 원주시 혁신로 19 지하층 101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1149,7 +1161,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 26 4층</t>
+          <t>강원 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4olwd</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1243,7 +1259,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
+          <t>강원 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4loqz</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1286,10 +1306,10 @@
         <v>717</v>
       </c>
       <c r="Q9" t="n">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="R9" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -820,10 +820,10 @@
         <v>378</v>
       </c>
       <c r="Q4" t="n">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="R4" t="n">
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1237,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>클래식짐 PT 혁신점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>classicgym2749@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1313-2749</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원 원주시 황금로 20 5층 502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://blog.naver.com/classicgym2749</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
+          <t>https://talk.naver.com/ct/w4ae4e</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>717</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="n">
-        <v>727</v>
+        <v>84</v>
       </c>
       <c r="R9" t="n">
-        <v>1444</v>
+        <v>160</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1324878145</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1324878145</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -628,10 +628,10 @@
         <v>235</v>
       </c>
       <c r="Q2" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="R2" t="n">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1230,41 +1230,41 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>클래식짐 PT 혁신점</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>classicgym2749@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1313-2749</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 황금로 20 5층 502호</t>
+          <t>강원 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/classicgym2749</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ae4e</t>
+          <t>https://talk.naver.com/ct/w4loqz</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>76</v>
+        <v>716</v>
       </c>
       <c r="Q9" t="n">
-        <v>84</v>
+        <v>729</v>
       </c>
       <c r="R9" t="n">
-        <v>160</v>
+        <v>1445</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1324878145</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324878145</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q3" t="n">
         <v>864</v>
       </c>
       <c r="R3" t="n">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         <v>378</v>
       </c>
       <c r="Q4" t="n">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="R4" t="n">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀키스짐 &amp; PT</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teamkis_@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1399-2305</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 26 4층</t>
+          <t>강원 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamkis_</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4olwd</t>
+          <t>https://talk.naver.com/ct/w4loqz</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2327</v>
+        <v>717</v>
       </c>
       <c r="Q8" t="n">
-        <v>500</v>
+        <v>732</v>
       </c>
       <c r="R8" t="n">
-        <v>2827</v>
+        <v>1449</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1433616376</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433616376</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>클래식짐 PT 혁신점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>classicgym2749@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1313-2749</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원 원주시 황금로 20 5층 502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://blog.naver.com/classicgym2749</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
+          <t>https://talk.naver.com/ct/w4ae4e</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>716</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="n">
-        <v>729</v>
+        <v>84</v>
       </c>
       <c r="R9" t="n">
-        <v>1445</v>
+        <v>160</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1324878145</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1324878145</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h9q7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,7 +752,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>비브레 PT/헬스 혁신점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -773,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q4" t="n">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="R4" t="n">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -871,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4047s</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -969,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 혁신로 19 지하층 101호</t>
+          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1034,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1186,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="Q8" t="n">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="R8" t="n">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1230,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 황금로 20 5층 502호</t>
+          <t>강원특별자치도 원주시 황금로 20 5층 502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1284,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ae4e</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1328,7 +1308,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h9q7</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -752,7 +756,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비브레 PT/헬스 혁신점</t>
+          <t>비브레 PT\u002F헬스 혁신점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eja</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +820,10 @@
         <v>379</v>
       </c>
       <c r="Q4" t="n">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="R4" t="n">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +881,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4047s</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>혁신런앤핏</t>
+          <t>블랑꼬 PT&amp;헬스 태장점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hghghghg00@naver.com</t>
+          <t>dlarhkddbf1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1346-7262</t>
+          <t>0507-1330-4023</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
+          <t>강원 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hs_run_fit</t>
+          <t>https://blog.naver.com/dlarhkddbf1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,18 +989,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43uav</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="R6" t="n">
-        <v>23</v>
+        <v>144</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1223719800</t>
+          <t>1901538636</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223719800</t>
+          <t>https://m.place.naver.com/place/1901538636</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1132,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>팀키스짐 &amp; PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>teamkis_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1399-2305</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
+          <t>강원 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://blog.naver.com/teamkis_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4olwd</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>721</v>
+        <v>2331</v>
       </c>
       <c r="Q8" t="n">
-        <v>731</v>
+        <v>503</v>
       </c>
       <c r="R8" t="n">
-        <v>1452</v>
+        <v>2834</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1433616376</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1433616376</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>클래식짐 PT 혁신점</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>classicgym2749@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1313-2749</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 황금로 20 5층 502호</t>
+          <t>강원 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/classicgym2749</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1268,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4loqz</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>76</v>
+        <v>724</v>
       </c>
       <c r="Q9" t="n">
-        <v>84</v>
+        <v>733</v>
       </c>
       <c r="R9" t="n">
-        <v>160</v>
+        <v>1457</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1324878145</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324878145</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h9q7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -628,10 +624,10 @@
         <v>235</v>
       </c>
       <c r="Q2" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="R2" t="n">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -756,7 +752,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>비브레 PT/헬스 혁신점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -773,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q4" t="n">
         <v>2190</v>
       </c>
       <c r="R4" t="n">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -871,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -881,7 +873,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4047s</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -969,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
+          <t>강원특별자치도 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43uav</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1038,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 26 4층</t>
+          <t>강원특별자치도 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4olwd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1212,10 +1192,10 @@
         <v>2331</v>
       </c>
       <c r="Q8" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R8" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1288,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="Q9" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="R9" t="n">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1332,7 +1308,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_PT.xlsx
+++ b/naver-place-crawler/results_health/원주_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h9q7</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
+          <t>강원 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -752,7 +756,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비브레 PT/헬스 혁신점</t>
+          <t>비브레 PT\u002F헬스 혁신점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eja</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4047s</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
+          <t>강원 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43uav</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1132,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀키스짐 &amp; PT</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teamkis_@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1399-2305</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 26 4층</t>
+          <t>강원 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamkis_</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4loqz</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2331</v>
+        <v>726</v>
       </c>
       <c r="Q8" t="n">
-        <v>504</v>
+        <v>737</v>
       </c>
       <c r="R8" t="n">
-        <v>2835</v>
+        <v>1463</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1433616376</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433616376</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>클래식짐 PT 혁신점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>classicgym2749@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1313-2749</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
+          <t>강원 원주시 황금로 20 5층 502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://blog.naver.com/classicgym2749</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1268,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ae4e</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>726</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="n">
-        <v>734</v>
+        <v>84</v>
       </c>
       <c r="R9" t="n">
-        <v>1460</v>
+        <v>160</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1324878145</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1324878145</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
